--- a/data/trans_orig/P19C01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>66136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>60069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87576</t>
+          <t>87934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108604</t>
+          <t>107009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146220</t>
+          <t>145568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125505</t>
+          <t>125357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149603</t>
+          <t>149197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113646</t>
+          <t>113288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141759</t>
+          <t>141153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246496</t>
+          <t>247148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284112</t>
+          <t>285707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103480</t>
+          <t>101624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143124</t>
+          <t>142154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113359</t>
+          <t>111261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150898</t>
+          <t>149439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227642</t>
+          <t>225379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281185</t>
+          <t>280499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266632</t>
+          <t>267602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306276</t>
+          <t>308132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290303</t>
+          <t>291762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327842</t>
+          <t>329940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>569772</t>
+          <t>570458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>623315</t>
+          <t>625578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>43862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71030</t>
+          <t>70074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59545</t>
+          <t>57490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>86888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111596</t>
+          <t>109988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151822</t>
+          <t>149800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165507</t>
+          <t>166463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191239</t>
+          <t>192675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199352</t>
+          <t>201918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229261</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373521</t>
+          <t>375543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>413747</t>
+          <t>415355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>84025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113405</t>
+          <t>114298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90363</t>
+          <t>89899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121510</t>
+          <t>121124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181301</t>
+          <t>180023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225864</t>
+          <t>225134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154126</t>
+          <t>153233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185218</t>
+          <t>183506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178024</t>
+          <t>178410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209171</t>
+          <t>209635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341201</t>
+          <t>341931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>385764</t>
+          <t>387042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>80614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61929</t>
+          <t>61966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124721</t>
+          <t>125243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160520</t>
+          <t>162369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88863</t>
+          <t>89664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114396</t>
+          <t>115119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85569</t>
+          <t>86020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111977</t>
+          <t>111940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183664</t>
+          <t>181815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219463</t>
+          <t>218941</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60079</t>
+          <t>58350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>51597</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>78292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92871</t>
+          <t>94325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128242</t>
+          <t>129831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129191</t>
+          <t>130920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153160</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125668</t>
+          <t>126196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151966</t>
+          <t>152891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265516</t>
+          <t>263927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300887</t>
+          <t>299433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84035</t>
+          <t>83657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120199</t>
+          <t>120976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120160</t>
+          <t>119821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160218</t>
+          <t>161677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216665</t>
+          <t>214821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>271193</t>
+          <t>270757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>344126</t>
+          <t>343349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>380290</t>
+          <t>380668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379150</t>
+          <t>377691</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>419208</t>
+          <t>419547</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>732499</t>
+          <t>732935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>787027</t>
+          <t>788871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165489</t>
+          <t>163257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>208955</t>
+          <t>206130</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176635</t>
+          <t>173330</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>222892</t>
+          <t>220979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>355159</t>
+          <t>354139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>415631</t>
+          <t>416589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>318100</t>
+          <t>320925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>361566</t>
+          <t>363798</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>368589</t>
+          <t>370502</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>414846</t>
+          <t>418151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>702905</t>
+          <t>701947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>763377</t>
+          <t>764397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>692031</t>
+          <t>687407</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>776288</t>
+          <t>777003</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>813224</t>
+          <t>813931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>914498</t>
+          <t>907265</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1528215</t>
+          <t>1525596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1660205</t>
+          <t>1658507</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1679957</t>
+          <t>1679242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1764214</t>
+          <t>1768838</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1825508</t>
+          <t>1832741</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1926782</t>
+          <t>1926075</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3536047</t>
+          <t>3537745</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3668037</t>
+          <t>3670656</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59387</t>
+          <t>58809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57768</t>
+          <t>57597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74432</t>
+          <t>73508</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109855</t>
+          <t>110202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191173</t>
+          <t>191751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215530</t>
+          <t>215390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192513</t>
+          <t>192684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216755</t>
+          <t>218036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390987</t>
+          <t>390640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426410</t>
+          <t>427334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100321</t>
+          <t>98348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138562</t>
+          <t>138740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110292</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>148385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221350</t>
+          <t>219018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275703</t>
+          <t>276166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267768</t>
+          <t>267590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306009</t>
+          <t>307982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288843</t>
+          <t>288440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326533</t>
+          <t>329086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>567452</t>
+          <t>566989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>621805</t>
+          <t>624137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82450</t>
+          <t>82267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114329</t>
+          <t>114987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>101012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135611</t>
+          <t>136480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193877</t>
+          <t>194183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240737</t>
+          <t>243076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179335</t>
+          <t>178677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211214</t>
+          <t>211397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>192070</t>
+          <t>191201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>226019</t>
+          <t>226669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380608</t>
+          <t>378269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>427468</t>
+          <t>427162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75926</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111531</t>
+          <t>110944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105332</t>
+          <t>106070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142707</t>
+          <t>143120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191965</t>
+          <t>193173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241484</t>
+          <t>244221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201546</t>
+          <t>202133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237151</t>
+          <t>237179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200108</t>
+          <t>199695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237483</t>
+          <t>236745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414407</t>
+          <t>411670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>463926</t>
+          <t>462718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>62194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91166</t>
+          <t>89491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76447</t>
+          <t>76191</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104083</t>
+          <t>104854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145764</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187131</t>
+          <t>184673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100892</t>
+          <t>102567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129898</t>
+          <t>129864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>89728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118135</t>
+          <t>118391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>199509</t>
+          <t>201967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240876</t>
+          <t>242120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>62054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91587</t>
+          <t>91072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>90193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>120666</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157683</t>
+          <t>157082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202217</t>
+          <t>200900</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158386</t>
+          <t>158901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188129</t>
+          <t>187919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146061</t>
+          <t>144164</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176713</t>
+          <t>174637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312586</t>
+          <t>313903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>357120</t>
+          <t>357721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153254</t>
+          <t>152661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201889</t>
+          <t>197784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222429</t>
+          <t>223740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272467</t>
+          <t>272845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386875</t>
+          <t>390473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457977</t>
+          <t>457595</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>373202</t>
+          <t>377307</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>421837</t>
+          <t>422430</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>353520</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>403558</t>
+          <t>402247</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>743101</t>
+          <t>743483</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>814203</t>
+          <t>810605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147936</t>
+          <t>150738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>195826</t>
+          <t>196151</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197407</t>
+          <t>198211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>251263</t>
+          <t>247460</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>360233</t>
+          <t>364669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>430834</t>
+          <t>432449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>438079</t>
+          <t>437754</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>483167</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>451031</t>
+          <t>454834</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>504887</t>
+          <t>504083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>905365</t>
+          <t>903750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>975966</t>
+          <t>971530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>803968</t>
+          <t>809706</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>910699</t>
+          <t>913371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1023560</t>
+          <t>1023692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1132517</t>
+          <t>1131777</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1851991</t>
+          <t>1863103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2006171</t>
+          <t>2017148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2003960</t>
+          <t>2001288</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2110691</t>
+          <t>2104953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2012778</t>
+          <t>2013518</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2121735</t>
+          <t>2121603</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4053782</t>
+          <t>4042805</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4207962</t>
+          <t>4196850</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46203</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74928</t>
+          <t>74280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63801</t>
+          <t>63487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92923</t>
+          <t>93399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117415</t>
+          <t>119003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158753</t>
+          <t>159417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170290</t>
+          <t>170938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199015</t>
+          <t>199730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153411</t>
+          <t>152935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182533</t>
+          <t>182847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>332798</t>
+          <t>332134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374136</t>
+          <t>372548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81213</t>
+          <t>81879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114777</t>
+          <t>116888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117682</t>
+          <t>117754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155709</t>
+          <t>153776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207969</t>
+          <t>208262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259316</t>
+          <t>260528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248388</t>
+          <t>246277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>281952</t>
+          <t>281286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237618</t>
+          <t>239551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275645</t>
+          <t>275573</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497176</t>
+          <t>495964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>548523</t>
+          <t>548230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93767</t>
+          <t>91517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125813</t>
+          <t>125703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104865</t>
+          <t>104974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138766</t>
+          <t>138623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206858</t>
+          <t>206982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255776</t>
+          <t>254409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164694</t>
+          <t>164804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196740</t>
+          <t>198990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168998</t>
+          <t>169141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202899</t>
+          <t>202790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>343861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>391412</t>
+          <t>391288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84281</t>
+          <t>83895</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118713</t>
+          <t>118409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>76785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111052</t>
+          <t>110295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171182</t>
+          <t>171559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218984</t>
+          <t>222256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211334</t>
+          <t>211638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245766</t>
+          <t>246152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>237809</t>
+          <t>238566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271170</t>
+          <t>272076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459924</t>
+          <t>456652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507726</t>
+          <t>507349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>66141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86521</t>
+          <t>87230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88841</t>
+          <t>87458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110452</t>
+          <t>108976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159730</t>
+          <t>160292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190451</t>
+          <t>189410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>58042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74271</t>
+          <t>75312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104992</t>
+          <t>104430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>77146</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>107594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95549</t>
+          <t>96153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125989</t>
+          <t>127726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183840</t>
+          <t>182122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>227384</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126142</t>
+          <t>126021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156491</t>
+          <t>156469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121148</t>
+          <t>119411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151588</t>
+          <t>150984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253369</t>
+          <t>254617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296913</t>
+          <t>298631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199673</t>
+          <t>196207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242673</t>
+          <t>241334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218466</t>
+          <t>216147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>263143</t>
+          <t>262027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>430749</t>
+          <t>426626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>493380</t>
+          <t>491546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199634</t>
+          <t>200973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242634</t>
+          <t>246100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223908</t>
+          <t>225024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268585</t>
+          <t>270904</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>435978</t>
+          <t>437812</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>498609</t>
+          <t>502732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>303076</t>
+          <t>301620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>356477</t>
+          <t>354148</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>335898</t>
+          <t>342165</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>391462</t>
+          <t>395464</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>662516</t>
+          <t>659270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>734108</t>
+          <t>732212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>283775</t>
+          <t>286104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>337176</t>
+          <t>338632</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299879</t>
+          <t>295877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>355443</t>
+          <t>349176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>597485</t>
+          <t>599381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>669077</t>
+          <t>672323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1037677</t>
+          <t>1032978</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1143813</t>
+          <t>1137089</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1191683</t>
+          <t>1193046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1299392</t>
+          <t>1302499</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2254138</t>
+          <t>2258370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2403527</t>
+          <t>2401253</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1520520</t>
+          <t>1527244</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1626656</t>
+          <t>1631355</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1567923</t>
+          <t>1564816</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1675632</t>
+          <t>1674269</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3128121</t>
+          <t>3130395</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3277510</t>
+          <t>3273278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278623</t>
+          <t>278707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294217</t>
+          <t>294157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267126</t>
+          <t>267090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>277809</t>
+          <t>277731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>550670</t>
+          <t>550679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>569038</t>
+          <t>569640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176365</t>
+          <t>176671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232431</t>
+          <t>231550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>190762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229283</t>
+          <t>229127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>376020</t>
+          <t>379633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274553</t>
+          <t>275434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330619</t>
+          <t>330313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272265</t>
+          <t>272421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311659</t>
+          <t>310786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>632512</t>
+          <t>628899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108753</t>
+          <t>109675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144611</t>
+          <t>144135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125222</t>
+          <t>124592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157708</t>
+          <t>155986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>243906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292932</t>
+          <t>289965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156581</t>
+          <t>157057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192439</t>
+          <t>191517</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177567</t>
+          <t>179289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210053</t>
+          <t>210683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343535</t>
+          <t>346502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>394508</t>
+          <t>392561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,68%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80985</t>
+          <t>80120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122251</t>
+          <t>121726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130721</t>
+          <t>128536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305632</t>
+          <t>303113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233048</t>
+          <t>227198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422556</t>
+          <t>413150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187869</t>
+          <t>188394</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229135</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167833</t>
+          <t>170352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>342744</t>
+          <t>344929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361029</t>
+          <t>370435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550537</t>
+          <t>556387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143028</t>
+          <t>144377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155322</t>
+          <t>155729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176052</t>
+          <t>175873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187497</t>
+          <t>187627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324482</t>
+          <t>325182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340810</t>
+          <t>340521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46239</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92438</t>
+          <t>93106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123945</t>
+          <t>122900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114814</t>
+          <t>114897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138877</t>
+          <t>139839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>216040</t>
+          <t>214474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>255084</t>
+          <t>254698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129787</t>
+          <t>130832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161294</t>
+          <t>160626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131536</t>
+          <t>131453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244998</t>
+          <t>245384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284042</t>
+          <t>285608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>329615</t>
+          <t>330173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>382437</t>
+          <t>382762</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172156</t>
+          <t>164268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>485145</t>
+          <t>485631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>444028</t>
+          <t>447863</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>848841</t>
+          <t>847552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217962</t>
+          <t>217637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270784</t>
+          <t>270226</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343220</t>
+          <t>342734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>656209</t>
+          <t>664097</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>579924</t>
+          <t>581213</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>984737</t>
+          <t>980902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>195825</t>
+          <t>211923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>630886</t>
+          <t>630934</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>496698</t>
+          <t>498874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>537773</t>
+          <t>540764</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>550046</t>
+          <t>606284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1158807</t>
+          <t>1157496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277753</t>
+          <t>277705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>712814</t>
+          <t>696716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166151</t>
+          <t>163160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>205050</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>453756</t>
+          <t>455067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1062517</t>
+          <t>1006279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1376402</t>
+          <t>1400399</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1951046</t>
+          <t>1951534</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1585742</t>
+          <t>1587861</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2149709</t>
+          <t>2147506</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3318150</t>
+          <t>3328718</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4056925</t>
+          <t>4020537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1403880</t>
+          <t>1403392</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1978524</t>
+          <t>1954527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1429118</t>
+          <t>1431321</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1993085</t>
+          <t>1990966</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2876827</t>
+          <t>2913215</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3615602</t>
+          <t>3605034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42296</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66136</t>
+          <t>66980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60069</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87934</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107009</t>
+          <t>108169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145568</t>
+          <t>145596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125357</t>
+          <t>124513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149197</t>
+          <t>149563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113288</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141153</t>
+          <t>141740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247148</t>
+          <t>247120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285707</t>
+          <t>284547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101624</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142154</t>
+          <t>142093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>110392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>150258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>225379</t>
+          <t>227043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280499</t>
+          <t>279423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267602</t>
+          <t>267663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308132</t>
+          <t>306307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291762</t>
+          <t>290943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329940</t>
+          <t>330809</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570458</t>
+          <t>571534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>625578</t>
+          <t>623914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43862</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70074</t>
+          <t>69335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57490</t>
+          <t>60506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86888</t>
+          <t>88628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109988</t>
+          <t>109083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149800</t>
+          <t>150115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166463</t>
+          <t>167202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192675</t>
+          <t>193163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201918</t>
+          <t>200178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375543</t>
+          <t>375228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>415355</t>
+          <t>416260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84025</t>
+          <t>83271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114298</t>
+          <t>114689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89899</t>
+          <t>89977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121124</t>
+          <t>122066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180023</t>
+          <t>180016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225134</t>
+          <t>226404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153233</t>
+          <t>152842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183506</t>
+          <t>184260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178410</t>
+          <t>177468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209635</t>
+          <t>209557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341931</t>
+          <t>340661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387042</t>
+          <t>387049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55159</t>
+          <t>55351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80614</t>
+          <t>80651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61966</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>87021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125243</t>
+          <t>123933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162369</t>
+          <t>161432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89664</t>
+          <t>89627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115119</t>
+          <t>114927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86020</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111940</t>
+          <t>112915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181815</t>
+          <t>182752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218941</t>
+          <t>220251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58350</t>
+          <t>61984</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51597</t>
+          <t>52234</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>79161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94325</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129831</t>
+          <t>128787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130920</t>
+          <t>127286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154519</t>
+          <t>153610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126196</t>
+          <t>125327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152891</t>
+          <t>152254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263927</t>
+          <t>264971</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299433</t>
+          <t>299461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83657</t>
+          <t>85991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120976</t>
+          <t>120707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119821</t>
+          <t>119998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161677</t>
+          <t>160324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214821</t>
+          <t>214146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270757</t>
+          <t>270364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>343349</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>380668</t>
+          <t>378334</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377691</t>
+          <t>379044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>419547</t>
+          <t>419370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>732935</t>
+          <t>733328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788871</t>
+          <t>789546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163257</t>
+          <t>165245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206130</t>
+          <t>206415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>173330</t>
+          <t>176431</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220979</t>
+          <t>225308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354139</t>
+          <t>353052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>416589</t>
+          <t>416514</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>320925</t>
+          <t>320640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>363798</t>
+          <t>361810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>370502</t>
+          <t>366173</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>418151</t>
+          <t>415050</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>701947</t>
+          <t>702022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>764397</t>
+          <t>765484</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>687407</t>
+          <t>687219</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>777003</t>
+          <t>780082</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>813931</t>
+          <t>812786</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>907265</t>
+          <t>908419</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1525596</t>
+          <t>1521653</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1658507</t>
+          <t>1660640</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1679242</t>
+          <t>1676163</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1768838</t>
+          <t>1769026</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1832741</t>
+          <t>1831587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1926075</t>
+          <t>1927220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3537745</t>
+          <t>3535612</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3670656</t>
+          <t>3674599</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,72%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>59670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73508</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110202</t>
+          <t>111695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191751</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215390</t>
+          <t>214290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192684</t>
+          <t>193354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218036</t>
+          <t>217583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390640</t>
+          <t>389147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427334</t>
+          <t>426491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98348</t>
+          <t>102298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138740</t>
+          <t>140225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107739</t>
+          <t>109306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148385</t>
+          <t>147642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219018</t>
+          <t>219298</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276166</t>
+          <t>274552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267590</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307982</t>
+          <t>304032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288440</t>
+          <t>289183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329086</t>
+          <t>327519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>566989</t>
+          <t>568603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624137</t>
+          <t>623857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82267</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114987</t>
+          <t>116626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136480</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194183</t>
+          <t>192337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243076</t>
+          <t>241866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178677</t>
+          <t>177038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211397</t>
+          <t>208984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191201</t>
+          <t>189101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>226669</t>
+          <t>225411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378269</t>
+          <t>379479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>427162</t>
+          <t>429008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75898</t>
+          <t>76826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110944</t>
+          <t>112519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106070</t>
+          <t>103987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143120</t>
+          <t>141763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193173</t>
+          <t>190822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244221</t>
+          <t>241033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202133</t>
+          <t>200558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237179</t>
+          <t>236251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199695</t>
+          <t>201052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236745</t>
+          <t>238828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411670</t>
+          <t>414858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>462718</t>
+          <t>465069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62194</t>
+          <t>62397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89491</t>
+          <t>90040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76191</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104854</t>
+          <t>103610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144520</t>
+          <t>146667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>184673</t>
+          <t>185847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102567</t>
+          <t>102018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129864</t>
+          <t>129661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89728</t>
+          <t>90972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118391</t>
+          <t>119421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201967</t>
+          <t>200793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242120</t>
+          <t>239973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91072</t>
+          <t>92376</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90193</t>
+          <t>87601</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>118753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157082</t>
+          <t>158792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200900</t>
+          <t>199663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158901</t>
+          <t>157597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187919</t>
+          <t>187557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144164</t>
+          <t>146077</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174637</t>
+          <t>177229</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313903</t>
+          <t>315140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>357721</t>
+          <t>356011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152661</t>
+          <t>152740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197784</t>
+          <t>202109</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223740</t>
+          <t>221911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272845</t>
+          <t>272713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390473</t>
+          <t>386030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457595</t>
+          <t>456825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377307</t>
+          <t>372982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>422430</t>
+          <t>422351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>353142</t>
+          <t>353274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402247</t>
+          <t>404076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>743483</t>
+          <t>744253</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>810605</t>
+          <t>815048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150738</t>
+          <t>149935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196151</t>
+          <t>194681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198211</t>
+          <t>196039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>247460</t>
+          <t>246672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>364669</t>
+          <t>365204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>432449</t>
+          <t>431831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>437754</t>
+          <t>439224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>483167</t>
+          <t>483970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>454834</t>
+          <t>455622</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>504083</t>
+          <t>506255</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>903750</t>
+          <t>904368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>971530</t>
+          <t>970995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>809706</t>
+          <t>805087</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>913371</t>
+          <t>907853</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1023692</t>
+          <t>1019742</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1131777</t>
+          <t>1132844</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1863103</t>
+          <t>1864483</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2017148</t>
+          <t>2018008</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2001288</t>
+          <t>2006806</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2104953</t>
+          <t>2109572</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2013518</t>
+          <t>2012451</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2121603</t>
+          <t>2125553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4042805</t>
+          <t>4041945</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4196850</t>
+          <t>4195470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>46895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>75980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63487</t>
+          <t>62980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93399</t>
+          <t>92147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119003</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159417</t>
+          <t>160445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170938</t>
+          <t>169238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199730</t>
+          <t>198323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152935</t>
+          <t>154187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182847</t>
+          <t>183354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>331106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372548</t>
+          <t>373804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81879</t>
+          <t>82385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116888</t>
+          <t>116670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117754</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>153776</t>
+          <t>155329</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>208262</t>
+          <t>207668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260528</t>
+          <t>258709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246277</t>
+          <t>246495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>281286</t>
+          <t>280780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239551</t>
+          <t>237998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275573</t>
+          <t>276620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495964</t>
+          <t>497783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>548230</t>
+          <t>548824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91517</t>
+          <t>95012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125703</t>
+          <t>126831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>105047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138623</t>
+          <t>138228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206982</t>
+          <t>204496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254409</t>
+          <t>251804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164804</t>
+          <t>163676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>195495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169141</t>
+          <t>169536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202790</t>
+          <t>202717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343861</t>
+          <t>346466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>391288</t>
+          <t>393774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83895</t>
+          <t>83528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118409</t>
+          <t>117590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76785</t>
+          <t>79038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110295</t>
+          <t>112800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171559</t>
+          <t>171505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222256</t>
+          <t>220806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211638</t>
+          <t>212457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>246152</t>
+          <t>246519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>238566</t>
+          <t>236061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272076</t>
+          <t>269823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>456652</t>
+          <t>458102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507349</t>
+          <t>507403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66141</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87230</t>
+          <t>86971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87458</t>
+          <t>87298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108976</t>
+          <t>109408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160292</t>
+          <t>159635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189410</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53081</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58042</t>
+          <t>58202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>74875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104430</t>
+          <t>105087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77146</t>
+          <t>76735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>108339</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>95615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127726</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182122</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226136</t>
+          <t>227039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126021</t>
+          <t>125276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156469</t>
+          <t>156880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119411</t>
+          <t>119534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150984</t>
+          <t>151522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254617</t>
+          <t>253714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298631</t>
+          <t>298254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196207</t>
+          <t>199724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241334</t>
+          <t>240668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>216147</t>
+          <t>216769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262027</t>
+          <t>261680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>426626</t>
+          <t>430491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>491546</t>
+          <t>492097</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200973</t>
+          <t>201639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246100</t>
+          <t>242583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>225024</t>
+          <t>225371</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>270904</t>
+          <t>270282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437812</t>
+          <t>437261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>502732</t>
+          <t>498867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>301620</t>
+          <t>305259</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>354148</t>
+          <t>356042</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>342165</t>
+          <t>337963</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>395464</t>
+          <t>392738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>659270</t>
+          <t>659907</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>732212</t>
+          <t>733328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>286104</t>
+          <t>284210</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>338632</t>
+          <t>334993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>295877</t>
+          <t>298603</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>349176</t>
+          <t>353378</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>599381</t>
+          <t>598265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>672323</t>
+          <t>671686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1032978</t>
+          <t>1035993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1137089</t>
+          <t>1135352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1193046</t>
+          <t>1186673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1302499</t>
+          <t>1299243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2258370</t>
+          <t>2255915</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2401253</t>
+          <t>2411091</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1527244</t>
+          <t>1528981</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1631355</t>
+          <t>1628340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1564816</t>
+          <t>1568072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1674269</t>
+          <t>1680642</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3130395</t>
+          <t>3120557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3273278</t>
+          <t>3275733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>288007</t>
+          <t>276962</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278707</t>
+          <t>266531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294157</t>
+          <t>284294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>273202</t>
+          <t>293927</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267090</t>
+          <t>287485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>277731</t>
+          <t>299002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>561209</t>
+          <t>570888</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>550679</t>
+          <t>559643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>569640</t>
+          <t>581183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>34386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14405</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>39493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>203817</t>
+          <t>210788</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176671</t>
+          <t>186097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231550</t>
+          <t>240690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>209826</t>
+          <t>225345</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190762</t>
+          <t>205092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229127</t>
+          <t>246851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>413643</t>
+          <t>436133</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379633</t>
+          <t>399313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>447956</t>
+          <t>469267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>303167</t>
+          <t>307240</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275434</t>
+          <t>277338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330313</t>
+          <t>331931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>291722</t>
+          <t>306267</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272421</t>
+          <t>284761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>310786</t>
+          <t>326520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>594889</t>
+          <t>613507</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>560576</t>
+          <t>580373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>628899</t>
+          <t>650327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>126278</t>
+          <t>124013</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109675</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144135</t>
+          <t>140476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>140676</t>
+          <t>142626</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124592</t>
+          <t>127241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155986</t>
+          <t>158310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>266954</t>
+          <t>266639</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243906</t>
+          <t>243764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289965</t>
+          <t>291289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>174914</t>
+          <t>176218</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157057</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191517</t>
+          <t>192282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>194599</t>
+          <t>199079</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179289</t>
+          <t>183395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210683</t>
+          <t>214464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>369513</t>
+          <t>375296</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346502</t>
+          <t>350646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392561</t>
+          <t>398171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>101828</t>
+          <t>121164</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80120</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121726</t>
+          <t>149064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>188711</t>
+          <t>135470</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128536</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303113</t>
+          <t>154183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>290539</t>
+          <t>256635</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227198</t>
+          <t>227398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413150</t>
+          <t>289047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>208292</t>
+          <t>249574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188394</t>
+          <t>221674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>271661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>284754</t>
+          <t>284143</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170352</t>
+          <t>265430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>302906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>493046</t>
+          <t>533716</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370435</t>
+          <t>501304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556387</t>
+          <t>562953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>150421</t>
+          <t>165062</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144377</t>
+          <t>156806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>171879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>182811</t>
+          <t>198505</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175873</t>
+          <t>191972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187627</t>
+          <t>203591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>333232</t>
+          <t>363567</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>325182</t>
+          <t>353661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340521</t>
+          <t>372491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>36610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>55440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>107964</t>
+          <t>104288</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>90118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122900</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,67 +12447,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>126977</t>
+          <t>129515</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114897</t>
+          <t>117532</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139839</t>
+          <t>141928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>46,72%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>56,42%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>233802</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>213529</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>253870</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>46,64%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>56,76%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>234941</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>214474</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>254698</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>46,98%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>145768</t>
+          <t>145447</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130832</t>
+          <t>131510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160626</t>
+          <t>159617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,67 +12560,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119373</t>
+          <t>122045</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106511</t>
+          <t>109632</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131453</t>
+          <t>134028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>53,28%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>267492</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>247424</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>287765</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>53,36%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>265141</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>245384</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>285608</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>53,02%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>358151</t>
+          <t>411121</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>330173</t>
+          <t>380946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>382762</t>
+          <t>440458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>356420</t>
+          <t>418648</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164268</t>
+          <t>389703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>485631</t>
+          <t>442119</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>714572</t>
+          <t>829770</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>447863</t>
+          <t>790508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>847552</t>
+          <t>869712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>242248</t>
+          <t>287510</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217637</t>
+          <t>258173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270226</t>
+          <t>317685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>471945</t>
+          <t>322738</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>342734</t>
+          <t>299267</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>664097</t>
+          <t>351683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>714193</t>
+          <t>610248</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>581213</t>
+          <t>570306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>980902</t>
+          <t>649510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>698631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>698631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>698631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428765</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428765</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428765</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>454744</t>
+          <t>525933</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211923</t>
+          <t>498138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>630934</t>
+          <t>549823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>519216</t>
+          <t>599759</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>498874</t>
+          <t>578903</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>540764</t>
+          <t>622594</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>973959</t>
+          <t>1125692</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>606284</t>
+          <t>1095245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1157496</t>
+          <t>1160934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>453895</t>
+          <t>245117</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277705</t>
+          <t>221227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>696716</t>
+          <t>272912</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>184708</t>
+          <t>210548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>163160</t>
+          <t>187713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205050</t>
+          <t>231404</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>638604</t>
+          <t>455665</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>455067</t>
+          <t>420423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1006279</t>
+          <t>486112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1791211</t>
+          <t>1939330</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1400399</t>
+          <t>1872035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1951534</t>
+          <t>2002868</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>2143796</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1587861</t>
+          <t>2091003</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2147506</t>
+          <t>2197801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3789051</t>
+          <t>4083126</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3328718</t>
+          <t>3990974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4020537</t>
+          <t>4163549</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1563715</t>
+          <t>1459299</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1403392</t>
+          <t>1395761</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1954527</t>
+          <t>1526594</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1580986</t>
+          <t>1481652</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1431321</t>
+          <t>1427647</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1990966</t>
+          <t>1534445</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3144701</t>
+          <t>2940951</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2913215</t>
+          <t>2860528</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3605034</t>
+          <t>3033103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
